--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8727,6 +8727,33 @@
       <c r="G307" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="C308" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="D308" t="n">
+        <v>346.89</v>
+      </c>
+      <c r="E308" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="F308" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B321"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11954,6 +11981,16 @@
       </c>
       <c r="B321" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -12122,28 +12159,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2314195196660007</v>
+        <v>-0.2310609202635499</v>
       </c>
       <c r="J2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04249280971866543</v>
+        <v>0.04266349480460885</v>
       </c>
       <c r="M2" t="n">
-        <v>6.077842234536297</v>
+        <v>6.059748298572384</v>
       </c>
       <c r="N2" t="n">
-        <v>60.61623653899088</v>
+        <v>60.41967429580829</v>
       </c>
       <c r="O2" t="n">
-        <v>7.785642975309803</v>
+        <v>7.773009346180428</v>
       </c>
       <c r="P2" t="n">
-        <v>364.9332693918971</v>
+        <v>364.9293823379053</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12200,28 +12237,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01369838258537098</v>
+        <v>0.0137842324411031</v>
       </c>
       <c r="J3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002850551752717756</v>
+        <v>0.0002907529441215084</v>
       </c>
       <c r="M3" t="n">
-        <v>4.153934237149866</v>
+        <v>4.140870994318272</v>
       </c>
       <c r="N3" t="n">
-        <v>33.05584286152255</v>
+        <v>32.94821981655087</v>
       </c>
       <c r="O3" t="n">
-        <v>5.74942108925086</v>
+        <v>5.740053990734832</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3232275892259</v>
+        <v>353.3222970159396</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12278,28 +12315,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04962559850730148</v>
+        <v>0.04808013687775877</v>
       </c>
       <c r="J4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00514542974297727</v>
+        <v>0.004863367712422129</v>
       </c>
       <c r="M4" t="n">
-        <v>3.735750161454505</v>
+        <v>3.729834381071297</v>
       </c>
       <c r="N4" t="n">
-        <v>23.91728396711844</v>
+        <v>23.85581112703254</v>
       </c>
       <c r="O4" t="n">
-        <v>4.890530029262518</v>
+        <v>4.884241100420058</v>
       </c>
       <c r="P4" t="n">
-        <v>347.8530523922688</v>
+        <v>347.8698044915618</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12356,28 +12393,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1381173924976581</v>
+        <v>0.1351233000983064</v>
       </c>
       <c r="J5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05446213722688142</v>
+        <v>0.05242659019582463</v>
       </c>
       <c r="M5" t="n">
-        <v>3.230756006669433</v>
+        <v>3.232745122368623</v>
       </c>
       <c r="N5" t="n">
-        <v>16.6357882429308</v>
+        <v>16.6432804167965</v>
       </c>
       <c r="O5" t="n">
-        <v>4.078699332254193</v>
+        <v>4.079617680224031</v>
       </c>
       <c r="P5" t="n">
-        <v>353.5464984296884</v>
+        <v>353.5789530259124</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12434,28 +12471,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1432093295432611</v>
+        <v>0.1378955577112331</v>
       </c>
       <c r="J6" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K6" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05980074611553599</v>
+        <v>0.05544331137925562</v>
       </c>
       <c r="M6" t="n">
-        <v>3.264916061010473</v>
+        <v>3.279202021643193</v>
       </c>
       <c r="N6" t="n">
-        <v>16.19639353604892</v>
+        <v>16.33791411958033</v>
       </c>
       <c r="O6" t="n">
-        <v>4.024474317976066</v>
+        <v>4.042018569920273</v>
       </c>
       <c r="P6" t="n">
-        <v>343.4698326041858</v>
+        <v>343.5274314676251</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12493,7 +12530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23855,6 +23892,43 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-35.555521819623635,174.4742614118422</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-35.55603244643806,174.4749081192797</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-35.55655197352746,174.4755476348111</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-35.55698296078025,174.4763028960983</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-35.55730462435904,174.47713451381813</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8752,6 +8752,33 @@
         <v>339.46</v>
       </c>
       <c r="G308" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="C309" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="D309" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="E309" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="F309" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="G309" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8768,7 +8795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11991,6 +12018,16 @@
       </c>
       <c r="B322" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -12159,28 +12196,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2310609202635499</v>
+        <v>-0.2294659028887403</v>
       </c>
       <c r="J2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04266349480460885</v>
+        <v>0.04238571206565656</v>
       </c>
       <c r="M2" t="n">
-        <v>6.059748298572384</v>
+        <v>6.047661563801439</v>
       </c>
       <c r="N2" t="n">
-        <v>60.41967429580829</v>
+        <v>60.24103583656667</v>
       </c>
       <c r="O2" t="n">
-        <v>7.773009346180428</v>
+        <v>7.761509894122836</v>
       </c>
       <c r="P2" t="n">
-        <v>364.9293823379053</v>
+        <v>364.9120308326648</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12237,28 +12274,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0137842324411031</v>
+        <v>0.01476436857858932</v>
       </c>
       <c r="J3" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K3" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002907529441215084</v>
+        <v>0.0003359399644956573</v>
       </c>
       <c r="M3" t="n">
-        <v>4.140870994318272</v>
+        <v>4.132707775708597</v>
       </c>
       <c r="N3" t="n">
-        <v>32.94821981655087</v>
+        <v>32.8478642981523</v>
       </c>
       <c r="O3" t="n">
-        <v>5.740053990734832</v>
+        <v>5.731305636428082</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3222970159396</v>
+        <v>353.3116345381543</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12315,28 +12352,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04808013687775877</v>
+        <v>0.04751326731311373</v>
       </c>
       <c r="J4" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K4" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004863367712422129</v>
+        <v>0.004784204587851337</v>
       </c>
       <c r="M4" t="n">
-        <v>3.729834381071297</v>
+        <v>3.719989609239955</v>
       </c>
       <c r="N4" t="n">
-        <v>23.85581112703254</v>
+        <v>23.78057131082874</v>
       </c>
       <c r="O4" t="n">
-        <v>4.884241100420058</v>
+        <v>4.876532714011948</v>
       </c>
       <c r="P4" t="n">
-        <v>347.8698044915618</v>
+        <v>347.8759712207629</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12393,28 +12430,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1351233000983064</v>
+        <v>0.1329167005862109</v>
       </c>
       <c r="J5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05242659019582463</v>
+        <v>0.05107093771612492</v>
       </c>
       <c r="M5" t="n">
-        <v>3.232745122368623</v>
+        <v>3.231457660056149</v>
       </c>
       <c r="N5" t="n">
-        <v>16.6432804167965</v>
+        <v>16.62279291188719</v>
       </c>
       <c r="O5" t="n">
-        <v>4.079617680224031</v>
+        <v>4.077105948082192</v>
       </c>
       <c r="P5" t="n">
-        <v>353.5789530259124</v>
+        <v>353.6029576691235</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12471,28 +12508,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1378955577112331</v>
+        <v>0.1333558041777992</v>
       </c>
       <c r="J6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05544331137925562</v>
+        <v>0.05197264361287013</v>
       </c>
       <c r="M6" t="n">
-        <v>3.279202021643193</v>
+        <v>3.290188781897616</v>
       </c>
       <c r="N6" t="n">
-        <v>16.33791411958033</v>
+        <v>16.4268723121089</v>
       </c>
       <c r="O6" t="n">
-        <v>4.042018569920273</v>
+        <v>4.053007810516641</v>
       </c>
       <c r="P6" t="n">
-        <v>343.5274314676251</v>
+        <v>343.5768174859031</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12530,7 +12567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23929,6 +23966,43 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-35.55550933607507,174.47427409695754</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-35.55602335362702,174.47491734012277</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-35.55654211884369,174.47555745866367</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-35.556974062849406,174.4763084974957</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-35.5572955913601,174.4771375852369</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G309"/>
+  <dimension ref="A1:G311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8779,6 +8779,60 @@
         <v>340.5</v>
       </c>
       <c r="G309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="C310" t="n">
+        <v>359.77</v>
+      </c>
+      <c r="D310" t="n">
+        <v>354.04</v>
+      </c>
+      <c r="E310" t="n">
+        <v>353.71</v>
+      </c>
+      <c r="F310" t="n">
+        <v>343</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="C311" t="n">
+        <v>359.77</v>
+      </c>
+      <c r="D311" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="E311" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="F311" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="G311" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8795,7 +8849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12028,6 +12082,26 @@
       </c>
       <c r="B323" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -12196,28 +12270,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2294659028887403</v>
+        <v>-0.2125332914602138</v>
       </c>
       <c r="J2" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K2" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04238571206565656</v>
+        <v>0.03654409542923354</v>
       </c>
       <c r="M2" t="n">
-        <v>6.047661563801439</v>
+        <v>6.089031591735566</v>
       </c>
       <c r="N2" t="n">
-        <v>60.24103583656667</v>
+        <v>60.82139053773273</v>
       </c>
       <c r="O2" t="n">
-        <v>7.761509894122836</v>
+        <v>7.798806994517349</v>
       </c>
       <c r="P2" t="n">
-        <v>364.9120308326648</v>
+        <v>364.7260470898123</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12274,28 +12348,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01476436857858932</v>
+        <v>0.0230523635366735</v>
       </c>
       <c r="J3" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K3" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003359399644956573</v>
+        <v>0.0008250602495517567</v>
       </c>
       <c r="M3" t="n">
-        <v>4.132707775708597</v>
+        <v>4.149877516575962</v>
       </c>
       <c r="N3" t="n">
-        <v>32.8478642981523</v>
+        <v>32.86809785403963</v>
       </c>
       <c r="O3" t="n">
-        <v>5.731305636428082</v>
+        <v>5.733070543263848</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3116345381543</v>
+        <v>353.2206012256576</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12352,28 +12426,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04751326731311373</v>
+        <v>0.05238278173811108</v>
       </c>
       <c r="J4" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K4" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004784204587851337</v>
+        <v>0.005873679878128035</v>
       </c>
       <c r="M4" t="n">
-        <v>3.719989609239955</v>
+        <v>3.722191297483908</v>
       </c>
       <c r="N4" t="n">
-        <v>23.78057131082874</v>
+        <v>23.71899023755918</v>
       </c>
       <c r="O4" t="n">
-        <v>4.876532714011948</v>
+        <v>4.870214598717308</v>
       </c>
       <c r="P4" t="n">
-        <v>347.8759712207629</v>
+        <v>347.8225031553483</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12430,28 +12504,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1329167005862109</v>
+        <v>0.1272818285317593</v>
       </c>
       <c r="J5" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K5" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05107093771612492</v>
+        <v>0.04740665275180855</v>
       </c>
       <c r="M5" t="n">
-        <v>3.231457660056149</v>
+        <v>3.233800023065754</v>
       </c>
       <c r="N5" t="n">
-        <v>16.62279291188719</v>
+        <v>16.62604095820232</v>
       </c>
       <c r="O5" t="n">
-        <v>4.077105948082192</v>
+        <v>4.077504256061828</v>
       </c>
       <c r="P5" t="n">
-        <v>353.6029576691235</v>
+        <v>353.6648590078748</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12508,28 +12582,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1333558041777992</v>
+        <v>0.1266514018367886</v>
       </c>
       <c r="J6" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K6" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05197264361287013</v>
+        <v>0.04736552832280372</v>
       </c>
       <c r="M6" t="n">
-        <v>3.290188781897616</v>
+        <v>3.299993515439505</v>
       </c>
       <c r="N6" t="n">
-        <v>16.4268723121089</v>
+        <v>16.4767552855403</v>
       </c>
       <c r="O6" t="n">
-        <v>4.053007810516641</v>
+        <v>4.059156967344365</v>
       </c>
       <c r="P6" t="n">
-        <v>343.5768174859031</v>
+        <v>343.650467352844</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12567,7 +12641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G309"/>
+  <dimension ref="A1:G311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24003,6 +24077,80 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-35.55543984429831,174.47434471069477</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-35.55599107761289,174.47495007057967</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-35.55650200118704,174.47559745077646</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-35.556975585918664,174.47630753869802</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-35.55727387742005,174.4771449684525</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-35.55543984429831,174.47434471069477</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-35.55599107761289,174.47495007057967</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-35.556520732080564,174.47557877850574</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-35.5569868886956,174.476300423409</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-35.55728760063021,174.4771403022607</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G311"/>
+  <dimension ref="A1:G314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8821,7 +8821,7 @@
         <v>371.21</v>
       </c>
       <c r="C311" t="n">
-        <v>359.77</v>
+        <v>352.94</v>
       </c>
       <c r="D311" t="n">
         <v>351.36</v>
@@ -8833,6 +8833,87 @@
         <v>341.42</v>
       </c>
       <c r="G311" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="C312" t="n">
+        <v>351.83</v>
+      </c>
+      <c r="D312" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="E312" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="F312" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="C313" t="n">
+        <v>347.82</v>
+      </c>
+      <c r="D313" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="E313" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="F313" t="n">
+        <v>340.71</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>359.43</v>
+      </c>
+      <c r="C314" t="n">
+        <v>346.7</v>
+      </c>
+      <c r="D314" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="E314" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="F314" t="n">
+        <v>341.16</v>
+      </c>
+      <c r="G314" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8849,7 +8930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12102,6 +12183,36 @@
       </c>
       <c r="B325" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -12270,28 +12381,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2125332914602138</v>
+        <v>-0.2071294715799737</v>
       </c>
       <c r="J2" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K2" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03654409542923354</v>
+        <v>0.03543136284889692</v>
       </c>
       <c r="M2" t="n">
-        <v>6.089031591735566</v>
+        <v>6.056833193664611</v>
       </c>
       <c r="N2" t="n">
-        <v>60.82139053773273</v>
+        <v>60.3966506383761</v>
       </c>
       <c r="O2" t="n">
-        <v>7.798806994517349</v>
+        <v>7.771528204824074</v>
       </c>
       <c r="P2" t="n">
-        <v>364.7260470898123</v>
+        <v>364.6665763118232</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12348,28 +12459,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0230523635366735</v>
+        <v>0.008410957336267918</v>
       </c>
       <c r="J3" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K3" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008250602495517567</v>
+        <v>0.0001118001520258316</v>
       </c>
       <c r="M3" t="n">
-        <v>4.149877516575962</v>
+        <v>4.131071320909551</v>
       </c>
       <c r="N3" t="n">
-        <v>32.86809785403963</v>
+        <v>32.71776965467325</v>
       </c>
       <c r="O3" t="n">
-        <v>5.733070543263848</v>
+        <v>5.719944899618636</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2206012256576</v>
+        <v>353.3818629611091</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12426,28 +12537,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05238278173811108</v>
+        <v>0.0477744392916512</v>
       </c>
       <c r="J4" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K4" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005873679878128035</v>
+        <v>0.004973204148317256</v>
       </c>
       <c r="M4" t="n">
-        <v>3.722191297483908</v>
+        <v>3.715626054619569</v>
       </c>
       <c r="N4" t="n">
-        <v>23.71899023755918</v>
+        <v>23.61421253691741</v>
       </c>
       <c r="O4" t="n">
-        <v>4.870214598717308</v>
+        <v>4.859445702641136</v>
       </c>
       <c r="P4" t="n">
-        <v>347.8225031553483</v>
+        <v>347.8733450386391</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12504,28 +12615,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1272818285317593</v>
+        <v>0.1179426982095148</v>
       </c>
       <c r="J5" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K5" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04740665275180855</v>
+        <v>0.04136386769096079</v>
       </c>
       <c r="M5" t="n">
-        <v>3.233800023065754</v>
+        <v>3.242048890956275</v>
       </c>
       <c r="N5" t="n">
-        <v>16.62604095820232</v>
+        <v>16.67088106992619</v>
       </c>
       <c r="O5" t="n">
-        <v>4.077504256061828</v>
+        <v>4.082999028891164</v>
       </c>
       <c r="P5" t="n">
-        <v>353.6648590078748</v>
+        <v>353.7677662172665</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12582,28 +12693,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1266514018367886</v>
+        <v>0.1147993913057421</v>
       </c>
       <c r="J6" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K6" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04736552832280372</v>
+        <v>0.03933177591948844</v>
       </c>
       <c r="M6" t="n">
-        <v>3.299993515439505</v>
+        <v>3.324424316385848</v>
       </c>
       <c r="N6" t="n">
-        <v>16.4767552855403</v>
+        <v>16.64534579030693</v>
       </c>
       <c r="O6" t="n">
-        <v>4.059156967344365</v>
+        <v>4.079870805590163</v>
       </c>
       <c r="P6" t="n">
-        <v>343.650467352844</v>
+        <v>343.7810629489597</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12641,7 +12752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G311"/>
+  <dimension ref="A1:G314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24127,7 +24238,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>-35.55599107761289,174.47495007057967</t>
+          <t>-35.55603848517482,174.4749019955125</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -24146,6 +24257,117 @@
         </is>
       </c>
       <c r="G311" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-35.55547514501616,174.47430884005897</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-35.55604618976954,174.47489418242893</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-35.5565244363241,174.47557508585416</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-35.55698304094179,174.47630284563527</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-35.55728760063021,174.4771403022607</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-35.55551897614879,174.47426430122994</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-35.556074023481635,174.47486595677222</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-35.5565639948428,174.47553565110115</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-35.55699129758009,174.4762976479411</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-35.55729376738916,174.47713820542717</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-35.55552154221146,174.4742616937337</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-35.55608179748489,174.47485807329357</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-35.55656686038873,174.47553279451859</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-35.55698432352639,174.47630203822652</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-35.557289858879976,174.47713953440618</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G314"/>
+  <dimension ref="A1:G315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8916,6 +8916,33 @@
       <c r="G314" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>357.78</v>
+      </c>
+      <c r="C315" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="D315" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="E315" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="F315" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12213,6 +12240,16 @@
       </c>
       <c r="B328" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -12381,28 +12418,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2071294715799737</v>
+        <v>-0.2080326397735634</v>
       </c>
       <c r="J2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03543136284889692</v>
+        <v>0.03597825531617183</v>
       </c>
       <c r="M2" t="n">
-        <v>6.056833193664611</v>
+        <v>6.041782147435694</v>
       </c>
       <c r="N2" t="n">
-        <v>60.3966506383761</v>
+        <v>60.21010220474567</v>
       </c>
       <c r="O2" t="n">
-        <v>7.771528204824074</v>
+        <v>7.759516879596672</v>
       </c>
       <c r="P2" t="n">
-        <v>364.6665763118232</v>
+        <v>364.6765655940764</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12459,28 +12496,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008410957336267918</v>
+        <v>0.002872121322009193</v>
       </c>
       <c r="J3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001118001520258316</v>
+        <v>1.304569674731582e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.131071320909551</v>
+        <v>4.14147743844825</v>
       </c>
       <c r="N3" t="n">
-        <v>32.71776965467325</v>
+        <v>32.8316184006934</v>
       </c>
       <c r="O3" t="n">
-        <v>5.719944899618636</v>
+        <v>5.729888166508435</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3818629611091</v>
+        <v>353.4431239717308</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12537,28 +12574,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0477744392916512</v>
+        <v>0.043544825044277</v>
       </c>
       <c r="J4" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K4" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004973204148317256</v>
+        <v>0.00414287732086438</v>
       </c>
       <c r="M4" t="n">
-        <v>3.715626054619569</v>
+        <v>3.720906791505259</v>
       </c>
       <c r="N4" t="n">
-        <v>23.61421253691741</v>
+        <v>23.66615663283695</v>
       </c>
       <c r="O4" t="n">
-        <v>4.859445702641136</v>
+        <v>4.864787419079785</v>
       </c>
       <c r="P4" t="n">
-        <v>347.8733450386391</v>
+        <v>347.9201257056723</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12615,28 +12652,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1179426982095148</v>
+        <v>0.1143594641850559</v>
       </c>
       <c r="J5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04136386769096079</v>
+        <v>0.03905276721263773</v>
       </c>
       <c r="M5" t="n">
-        <v>3.242048890956275</v>
+        <v>3.247239530134911</v>
       </c>
       <c r="N5" t="n">
-        <v>16.67088106992619</v>
+        <v>16.70904487369017</v>
       </c>
       <c r="O5" t="n">
-        <v>4.082999028891164</v>
+        <v>4.087669858695804</v>
       </c>
       <c r="P5" t="n">
-        <v>353.7677662172665</v>
+        <v>353.8073977458164</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12693,28 +12730,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1147993913057421</v>
+        <v>0.1117033143197425</v>
       </c>
       <c r="J6" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K6" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03933177591948844</v>
+        <v>0.03743142567359659</v>
       </c>
       <c r="M6" t="n">
-        <v>3.324424316385848</v>
+        <v>3.328919098078509</v>
       </c>
       <c r="N6" t="n">
-        <v>16.64534579030693</v>
+        <v>16.66046437509166</v>
       </c>
       <c r="O6" t="n">
-        <v>4.079870805590163</v>
+        <v>4.081723211474739</v>
       </c>
       <c r="P6" t="n">
-        <v>343.7810629489597</v>
+        <v>343.8153063901153</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12752,7 +12789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G314"/>
+  <dimension ref="A1:G315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24373,6 +24410,43 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-35.555532985463216,174.47425006570793</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-35.556091584399006,174.47484814855494</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-35.55658055909522,174.47551913865777</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-35.55699298097235,174.4762965882169</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-35.55728082588092,174.47714260582393</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
